--- a/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
+++ b/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MYPC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\AI_Log\ai-audit-log-KhanhNV1374\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C495412D-220C-4D07-B45D-30E1DB914200}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F792AFA-9814-438F-B786-258B6D5AC9A3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="1" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -147,6 +147,96 @@
   </si>
   <si>
     <t>Architecture Analysis</t>
+  </si>
+  <si>
+    <t>Requirement Analysis</t>
+  </si>
+  <si>
+    <t>What actors and use cases are necessary for a restaurant procurement and logistics management platform?</t>
+  </si>
+  <si>
+    <t>The system should include several major actors based on the operational flow of the supply chain.
+1. Restaurant Manager
+Responsibilities:
+View ingredient catalog
+Compare suppliers
+Create purchase requests
+Track deliveries
+Confirm goods receipt
+View forecasting dashboards
+2. Supplier Staff
+Responsibilities:
+Publish products
+Manage inventory
+Accept or reject purchase requests
+Prepare shipments
+Generate tracking information
+3. Logistics Dispatcher
+Responsibilities:
+Assign delivery vehicles
+Group delivery orders
+Optimize delivery routes
+Monitor delivery operations
+4. Driver
+Responsibilities:
+Receive delivery tasks
+Navigate delivery routes
+Confirm delivery completion
+5. Platform Administrator
+Responsibilities:
+Manage users
+Approve suppliers
+Monitor KPIs
+Configure optimization rules
+6. AI Optimization Engine
+Responsibilities:
+Forecast demand
+Recommend suppliers
+Predict delays
+Optimize routes
+The use cases should reflect the interaction between these actors and the operational workflow of procurement and logistics management.</t>
+  </si>
+  <si>
+    <t>UI/UX Design</t>
+  </si>
+  <si>
+    <t>How should we organize screen flow and navigation for
+ multiple user roles in a supply chain management platform?</t>
+  </si>
+  <si>
+    <t>The best approach is to use a centralized dashboard architecture where the Home Page acts as the main navigation hub.
+After login:
+users are redirected to role-specific dashboards
+navigation menus are generated based on permissions
+each module contains its own screen hierarchy
+For example:
+Restaurant Manager Flow
+Home Page
+→ Procurement
+→ Forecast Dashboard
+→ Deliveries
+→ Analytics
+Supplier Flow
+Home Page
+→ Products
+→ Inventory
+→ Orders
+→ Shipments
+Logistics Flow
+Home Page
+→ Orders Management
+→ Route Optimization
+→ Vehicle Monitoring
+The screen flow should focus on:
+simple navigation
+minimal screen depth
+clear module separation
+consistent UI structure
+For SRS documentation, the screen flow should represent:
+page-to-page navigation
+screen hierarchy
+movement between modules
+instead of detailed business workflows.</t>
   </si>
 </sst>
 </file>
@@ -585,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="409.5">
+    <row r="2" spans="1:4" ht="399">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -639,9 +729,9 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="24.5" customWidth="1"/>
-    <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="158" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="41.625" customWidth="1"/>
+    <col min="4" max="4" width="102.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15">
@@ -658,21 +748,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="409.5">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="409.5">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">

--- a/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
+++ b/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\AI_Log\ai-audit-log-KhanhNV1374\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F792AFA-9814-438F-B786-258B6D5AC9A3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F824618-F11A-4F4A-ACD0-F37DDA062F2F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="1" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -237,6 +237,105 @@
 screen hierarchy
 movement between modules
 instead of detailed business workflows.</t>
+  </si>
+  <si>
+    <t>Database Design</t>
+  </si>
+  <si>
+    <t>What database entities are required for procurement, inventory, logistics, and delivery tracking in a fresh food supply chain system?</t>
+  </si>
+  <si>
+    <t>The database should be organized into several functional domains.
+Authentication &amp; User Management
+Core entities:
+Users
+Roles
+UserSessions
+Notifications
+Restaurant &amp; Supplier Management
+Core entities:
+Restaurants
+Suppliers
+Products
+ProductCategories
+ProductImages
+Procurement Management
+Core entities:
+PurchaseRequests
+PurchaseRequestItems
+SupplierResponses
+These entities support procurement workflows between restaurants and suppliers.
+Inventory Management
+Core entities:
+InventoryStocks
+InventoryMovements
+These tables track realtime inventory quantity and stock history.
+Logistics Management
+Core entities:
+Vehicles
+Drivers
+Routes
+Deliveries
+DeliveryStops
+DeliveryTrackingLogs
+These entities support:
+route management
+delivery assignment
+GPS tracking
+realtime monitoring
+AI &amp; Analytics
+Core entities:
+DemandForecasts
+SupplierRecommendations
+MarketTrends
+RiskAlerts
+These tables store prediction and recommendation data generated by AI modules.
+The relationships between entities should support realtime operational workflows across procurement, inventory, and logistics systems.</t>
+  </si>
+  <si>
+    <t>AI Feature Planning</t>
+  </si>
+  <si>
+    <t>Which AI features are realistic and suitable for a semester-scale fresh food supply chain management project?</t>
+  </si>
+  <si>
+    <t>For a semester-scale project, the AI features should be practical, implementable, and strongly connected to the business domain.
+The most realistic AI features are:
+1. Demand Forecasting
+Predict future ingredient demand using:
+historical procurement data
+seasonal trends
+weather information
+This feature is highly relevant and relatively feasible using models such as Prophet or regression models.
+2. Supplier Recommendation
+Recommend suppliers based on:
+pricing
+delivery performance
+reliability
+rating history
+This can be implemented using scoring algorithms or lightweight recommendation logic.
+3. Route Optimization
+Optimize delivery routes using:
+distance
+traffic conditions
+delivery priority
+Google OR-Tools is suitable for this type of optimization problem.
+4. Delivery Delay Prediction
+Estimate possible delays using:
+traffic data
+weather conditions
+historical delivery duration
+This feature improves delivery planning and operational visibility.
+Complex AI systems such as:
+computer vision
+realtime anomaly detection
+deep learning pipelines
+are generally too difficult for a semester-scale SDLC project unless the team has strong AI specialization and sufficient implementation time.
+The project should prioritize:
+feasibility
+integration quality
+operational usefulness
+instead of overly complex AI experimentation.</t>
   </si>
 </sst>
 </file>
@@ -821,35 +920,61 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="409.5">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="409.5">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="409.5">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="409.5">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="4"/>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
+++ b/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\AI_Log\ai-audit-log-KhanhNV1374\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F824618-F11A-4F4A-ACD0-F37DDA062F2F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4DFD37-E977-404E-8C6F-025665156EAE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="3" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="2" r:id="rId1"/>
     <sheet name="Week 2" sheetId="3" r:id="rId2"/>
     <sheet name="Week 3" sheetId="4" r:id="rId3"/>
-    <sheet name="Template" sheetId="1" r:id="rId4"/>
+    <sheet name="Week 4" sheetId="5" r:id="rId4"/>
+    <sheet name="Template" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -336,6 +337,24 @@
 integration quality
 operational usefulness
 instead of overly complex AI experimentation.</t>
+  </si>
+  <si>
+    <t>Supplier Product Management</t>
+  </si>
+  <si>
+    <t>I am currently implementing the supplier product management module for the FreshConnect platform using React, Node.js, and Microsoft SQL Server. Suppliers should be able to publish new products, edit existing products, remove unavailable products, and organize their product catalog efficiently. I also want the design to be scalable because additional product attributes may be added in the future. Based on these requirements, what database structure and application design would you recommend for managing supplier products?</t>
+  </si>
+  <si>
+    <t>The product management module should separate supplier information, product information, product categories, and inventory records into different entities. Each product should contain its basic information while inventory should be managed independently to avoid duplicated data. Product images should also be stored separately to support multiple images per product. I adopted this modular database structure because it improves maintainability and allows future expansion without major database redesign.</t>
+  </si>
+  <si>
+    <t>Product Image Management</t>
+  </si>
+  <si>
+    <t>FreshConnect allows suppliers to upload product images that will be displayed throughout the system. Since the project uses React for the frontend and Node.js for the backend, I am considering different methods for storing uploaded images. Should the images be stored directly in the database or inside the server's file system with only their paths saved in SQL Server? Which solution would provide better performance, easier maintenance, and simpler deployment for a university-scale project?</t>
+  </si>
+  <si>
+    <t>Storing uploaded images inside the server's uploads directory while saving only the relative file path in the database is generally more efficient. This reduces database size, simplifies image serving, and makes file management easier. I decided to store images in the backend uploads folder and keep only their relative paths in the database.</t>
   </si>
 </sst>
 </file>
@@ -982,6 +1001,59 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B544C0-E7B7-46ED-B1A6-ED80243C36D2}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="43.625" customWidth="1"/>
+    <col min="3" max="3" width="85" customWidth="1"/>
+    <col min="4" max="4" width="150.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="85.5">
+      <c r="A1" s="2">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="85.5">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.25"/>

--- a/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
+++ b/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\AI_Log\ai-audit-log-KhanhNV1374\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4DFD37-E977-404E-8C6F-025665156EAE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A10B89D-F6BE-4D61-B95D-EB5AA3E3B10C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="3" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="4" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="2" r:id="rId1"/>
     <sheet name="Week 2" sheetId="3" r:id="rId2"/>
     <sheet name="Week 3" sheetId="4" r:id="rId3"/>
     <sheet name="Week 4" sheetId="5" r:id="rId4"/>
-    <sheet name="Template" sheetId="1" r:id="rId5"/>
+    <sheet name="Week 5" sheetId="6" r:id="rId5"/>
+    <sheet name="Template" sheetId="1" r:id="rId6"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -1054,6 +1055,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B09796-28CC-4A05-8333-AC9FC13A3922}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.25"/>

--- a/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
+++ b/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\AI_Log\ai-audit-log-KhanhNV1374\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A10B89D-F6BE-4D61-B95D-EB5AA3E3B10C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFD1D90-107B-4846-8AFA-CE2CC59F4243}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="4" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="5" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,9 @@
     <sheet name="Week 3" sheetId="4" r:id="rId3"/>
     <sheet name="Week 4" sheetId="5" r:id="rId4"/>
     <sheet name="Week 5" sheetId="6" r:id="rId5"/>
-    <sheet name="Template" sheetId="1" r:id="rId6"/>
+    <sheet name="Week 6" sheetId="7" r:id="rId6"/>
+    <sheet name="Week 7" sheetId="8" r:id="rId7"/>
+    <sheet name="Template" sheetId="1" r:id="rId8"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -356,6 +358,24 @@
   </si>
   <si>
     <t>Storing uploaded images inside the server's uploads directory while saving only the relative file path in the database is generally more efficient. This reduces database size, simplifies image serving, and makes file management easier. I decided to store images in the backend uploads folder and keep only their relative paths in the database.</t>
+  </si>
+  <si>
+    <t>AI Demand Forecasting</t>
+  </si>
+  <si>
+    <t>FreshConnect includes an AI-assisted demand forecasting feature to help restaurant managers estimate future purchasing quantities. I would like the prediction to be based on operational business data rather than random estimations. Which business parameters should be collected from restaurants, suppliers, and external sources to improve prediction accuracy while keeping the model practical for a semester-scale software engineering project?</t>
+  </si>
+  <si>
+    <t>The forecasting model should consider historical purchasing quantities, reorder frequency, ingredient consumption rates, inventory levels, supplier lead time, seasonal demand, market prices, and restaurant operating trends. These parameters provide meaningful business insights while remaining realistic for implementation. I decided to design the AI module around these operational parameters.</t>
+  </si>
+  <si>
+    <t>AI Supplier Recommendation</t>
+  </si>
+  <si>
+    <t>One of the objectives of FreshConnect is to recommend the most suitable supplier when a restaurant creates a purchase request. Instead of selecting suppliers randomly or only comparing prices, I want the recommendation to evaluate multiple business factors. Which supplier performance indicators should be included in the recommendation process, and how should they be combined into a reliable recommendation score?</t>
+  </si>
+  <si>
+    <t>Supplier recommendations should evaluate supplier pricing, inventory availability, fulfillment rate, delivery performance, preparation time, supplier rating, and historical reliability. These factors can be weighted to calculate a recommendation score while leaving the final purchasing decision to the restaurant manager. I adopted this explainable recommendation approach instead of a fully automated decision.</t>
   </si>
 </sst>
 </file>
@@ -1003,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B544C0-E7B7-46ED-B1A6-ED80243C36D2}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="43.625" customWidth="1"/>
@@ -1011,43 +1031,47 @@
     <col min="4" max="4" width="150.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="85.5">
-      <c r="A1" s="2">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>36</v>
+    <row r="1" spans="1:4" ht="15">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="85.5">
       <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="85.5">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1056,6 +1080,63 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B09796-28CC-4A05-8333-AC9FC13A3922}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="25.125" customWidth="1"/>
+    <col min="3" max="3" width="57.625" customWidth="1"/>
+    <col min="4" max="4" width="95.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="99.75">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="99.75">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E74302E-CF3C-4274-92D6-B4F9556588AD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
@@ -1063,7 +1144,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9990ACE4-FFF4-4A83-AAAC-6E354B1DFDF8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.25"/>

--- a/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
+++ b/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\AI_Log\ai-audit-log-KhanhNV1374\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFD1D90-107B-4846-8AFA-CE2CC59F4243}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1F56AE-4D8C-4219-8DA0-0AA63FC822FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="5" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -376,6 +376,24 @@
   </si>
   <si>
     <t>Supplier recommendations should evaluate supplier pricing, inventory availability, fulfillment rate, delivery performance, preparation time, supplier rating, and historical reliability. These factors can be weighted to calculate a recommendation score while leaving the final purchasing decision to the restaurant manager. I adopted this explainable recommendation approach instead of a fully automated decision.</t>
+  </si>
+  <si>
+    <t>AI Route Optimization</t>
+  </si>
+  <si>
+    <t>AI Risk Detection</t>
+  </si>
+  <si>
+    <t>FreshConnect also includes logistics management where dispatchers assign vehicles and delivery routes. I would like the AI component to assist dispatchers by suggesting optimized routes instead of replacing human decisions completely. Which logistics parameters should be analyzed when generating route optimization suggestions, and how can the recommendations improve delivery efficiency?</t>
+  </si>
+  <si>
+    <t>Route optimization should consider delivery locations, grouped orders, vehicle capacity, traffic conditions, estimated travel time, delivery priorities, and fuel consumption. The AI should generate optimized route suggestions that reduce travel distance and delivery delays while allowing dispatchers to approve the final routes. I decided to implement AI as a decision-support tool rather than an autonomous controller.</t>
+  </si>
+  <si>
+    <t>Besides forecasting and route optimization, I would like FreshConnect to detect operational risks that may affect procurement and delivery activities. The system should notify users before problems become serious. Which types of operational risks should be monitored continuously, and what information should the AI use to generate useful alerts?</t>
+  </si>
+  <si>
+    <t>The AI should monitor inventory shortages, repeated delivery delays, supplier fulfillment problems, abnormal demand increases, cold-chain temperature violations, and unusual operational patterns. Risk alerts should be generated based on historical operational data together with real-time logistics information. I decided to integrate these alerts into the notification system for proactive decision-making.</t>
   </si>
 </sst>
 </file>
@@ -1137,9 +1155,57 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E74302E-CF3C-4274-92D6-B4F9556588AD}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="26.625" customWidth="1"/>
+    <col min="3" max="3" width="64" customWidth="1"/>
+    <col min="4" max="4" width="92.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="85.5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="71.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
+++ b/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\AI_Log\ai-audit-log-KhanhNV1374\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1F56AE-4D8C-4219-8DA0-0AA63FC822FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD6E77F-B65D-4041-ACE9-71A65C8896D9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="5" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="6" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -394,6 +394,24 @@
   </si>
   <si>
     <t>The AI should monitor inventory shortages, repeated delivery delays, supplier fulfillment problems, abnormal demand increases, cold-chain temperature violations, and unusual operational patterns. Risk alerts should be generated based on historical operational data together with real-time logistics information. I decided to integrate these alerts into the notification system for proactive decision-making.</t>
+  </si>
+  <si>
+    <t>The administrator dashboard should provide a complete overview of platform performance instead of displaying only raw database statistics. Since FreshConnect manages restaurants, suppliers, logistics, and AI-generated insights, I need suggestions for designing an informative dashboard. Which KPIs and visual components should be included so administrators can quickly evaluate system performance and identify operational issues?</t>
+  </si>
+  <si>
+    <t>The dashboard should display procurement volume, delivery success rate, supplier performance, inventory alerts, system activity, AI recommendations, and operational trends using KPI cards, charts, and summary widgets. I decided to organize the dashboard into several overview sections to improve readability and support faster management decisions.</t>
+  </si>
+  <si>
+    <t>Administrator Dashboard</t>
+  </si>
+  <si>
+    <t>Security &amp; Audit Logging</t>
+  </si>
+  <si>
+    <t>FreshConnect includes multiple user roles such as Restaurant Manager, Supplier Staff, Logistics Dispatcher, Driver, and Platform Administrator. Since different users perform important business operations, I would like to implement an audit logging mechanism to improve accountability and troubleshooting. Which user activities should be recorded, what information should each log contain, and how can the audit logs remain useful without becoming unnecessarily large?</t>
+  </si>
+  <si>
+    <t>Audit logs should record authentication events, profile updates, supplier approvals, purchase request submissions, inventory changes, delivery updates, role modifications, and administrator actions. Each log should include the user ID, action type, affected entity, timestamp, IP address, and a brief description. I decided to record only important business events so that the logs remain useful while avoiding excessive storage usage.</t>
   </si>
 </sst>
 </file>
@@ -1212,9 +1230,57 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9990ACE4-FFF4-4A83-AAAC-6E354B1DFDF8}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="24.625" customWidth="1"/>
+    <col min="3" max="3" width="64" customWidth="1"/>
+    <col min="4" max="4" width="95.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="99.75">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="99.75">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
+++ b/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\AI_Log\ai-audit-log-KhanhNV1374\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD6E77F-B65D-4041-ACE9-71A65C8896D9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D41911-1E2C-4BA1-9A96-682CE8B6ADB2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="6" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="7" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,8 @@
     <sheet name="Week 5" sheetId="6" r:id="rId5"/>
     <sheet name="Week 6" sheetId="7" r:id="rId6"/>
     <sheet name="Week 7" sheetId="8" r:id="rId7"/>
-    <sheet name="Template" sheetId="1" r:id="rId8"/>
+    <sheet name="Week 8" sheetId="9" r:id="rId8"/>
+    <sheet name="Template" sheetId="1" r:id="rId9"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="64">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -412,6 +413,24 @@
   </si>
   <si>
     <t>Audit logs should record authentication events, profile updates, supplier approvals, purchase request submissions, inventory changes, delivery updates, role modifications, and administrator actions. Each log should include the user ID, action type, affected entity, timestamp, IP address, and a brief description. I decided to record only important business events so that the logs remain useful while avoiding excessive storage usage.</t>
+  </si>
+  <si>
+    <t>AI Architecture Integration</t>
+  </si>
+  <si>
+    <t>AI Recommendation Explanation</t>
+  </si>
+  <si>
+    <t>FreshConnect now contains several AI-assisted features, including demand forecasting, supplier recommendation, route optimization, and operational risk detection. Instead of embedding all AI logic directly into the backend business services, I would like to design a scalable architecture that allows future AI models to be replaced or upgraded independently. Since the backend is implemented with Node.js and the frontend uses React, what software architecture would be appropriate for integrating multiple AI services while keeping the system maintainable and loosely coupled?</t>
+  </si>
+  <si>
+    <t>A service-oriented architecture is recommended, where each AI capability is implemented as an independent service or module with clearly defined interfaces. The backend business logic should communicate with these AI services through dedicated APIs instead of embedding AI algorithms directly into controllers. This approach separates business logic from AI processing, simplifies future model upgrades, and improves maintainability. I decided to organize the AI components as independent services so they can be developed and improved without affecting the rest of the application.</t>
+  </si>
+  <si>
+    <t>One concern with AI-generated recommendations is that users may not trust the results if they only see a final prediction without understanding why it was generated. For FreshConnect, restaurant managers should be able to understand why a supplier or purchasing quantity was recommended. How can I design AI outputs so that recommendations are explainable and transparent while keeping the user interface simple?</t>
+  </si>
+  <si>
+    <t>AI recommendations should be accompanied by short explanations describing the main factors that influenced the result, such as supplier reliability, delivery performance, current inventory level, historical purchasing patterns, or forecast confidence score. Instead of exposing complex machine learning details, the system should provide concise business-oriented explanations. I decided to display recommendation scores together with short reasoning so users can understand the AI suggestions before making their own decisions.</t>
   </si>
 </sst>
 </file>
@@ -1286,6 +1305,63 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F610389-B32B-45D3-A5BD-E20BD186E089}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="38.25" customWidth="1"/>
+    <col min="4" max="4" width="165.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="199.5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="156.75">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.25"/>

--- a/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
+++ b/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\AI_Log\ai-audit-log-KhanhNV1374\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D41911-1E2C-4BA1-9A96-682CE8B6ADB2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686F1A6C-DCFF-4EFC-A318-7C53C4EBCF2D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="7" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="8" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,8 @@
     <sheet name="Week 6" sheetId="7" r:id="rId6"/>
     <sheet name="Week 7" sheetId="8" r:id="rId7"/>
     <sheet name="Week 8" sheetId="9" r:id="rId8"/>
-    <sheet name="Template" sheetId="1" r:id="rId9"/>
+    <sheet name="Week 9" sheetId="10" r:id="rId9"/>
+    <sheet name="Template" sheetId="1" r:id="rId10"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="68">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -431,6 +432,18 @@
   </si>
   <si>
     <t>AI recommendations should be accompanied by short explanations describing the main factors that influenced the result, such as supplier reliability, delivery performance, current inventory level, historical purchasing patterns, or forecast confidence score. Instead of exposing complex machine learning details, the system should provide concise business-oriented explanations. I decided to display recommendation scores together with short reasoning so users can understand the AI suggestions before making their own decisions.</t>
+  </si>
+  <si>
+    <t>As more modules are integrated into FreshConnect, including authentication, procurement, logistics, inventory, notifications, and AI services, I am concerned about backend performance and database efficiency. What optimization techniques should be considered for a Node.js application with SQL Server to reduce response time while keeping the system scalable for future development?</t>
+  </si>
+  <si>
+    <t>Performance can be improved by optimizing SQL queries, creating appropriate indexes, implementing pagination, reducing unnecessary database requests, caching frequently accessed data, and separating heavy AI computations from normal API requests. Database normalization and proper API design also contribute to better scalability. I decided to optimize database indexes and keep AI-related processing independent from standard CRUD operations.</t>
+  </si>
+  <si>
+    <t>FreshConnect handles user accounts, supplier information, logistics operations, and AI-generated recommendations. Since different user roles access different system functions, I want to strengthen overall application security before deployment. Besides authentication and JWT authorization, what additional security practices should be implemented in both the backend and frontend to reduce common security risks?</t>
+  </si>
+  <si>
+    <t>Additional security measures include role-based access control, password hashing with a strong algorithm, input validation, SQL injection prevention through parameterized queries, secure HTTP headers, rate limiting, file upload validation, audit logging, and HTTPS communication. I decided to combine JWT authentication with role-based authorization, secure password hashing, and comprehensive audit logs to improve overall platform security.</t>
   </si>
 </sst>
 </file>
@@ -918,6 +931,93 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="20.875" customWidth="1"/>
+    <col min="2" max="2" width="26.875" customWidth="1"/>
+    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="71.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="71.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="71.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="85.5">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
   <dimension ref="A1:D5"/>
@@ -1362,17 +1462,16 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
-  <dimension ref="A1:E5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6F8D42B-C401-45D9-9047-38F31B81E6E1}">
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20.875" customWidth="1"/>
-    <col min="2" max="2" width="26.875" customWidth="1"/>
-    <col min="3" max="3" width="24.25" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="3" max="3" width="55.375" customWidth="1"/>
+    <col min="4" max="4" width="127" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15">
+    <row r="1" spans="1:4" ht="15">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -1385,62 +1484,33 @@
       <c r="D1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" ht="71.25">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="71.25">
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="71.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="85.5">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>15</v>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
+++ b/AI Audit Log_NguyenVietKhanh_DE181002.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\AI_Log\ai-audit-log-KhanhNV1374\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686F1A6C-DCFF-4EFC-A318-7C53C4EBCF2D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0552FD44-F34F-489F-9DC7-F6CA703432E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="8" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="11475" activeTab="9" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,8 @@
     <sheet name="Week 7" sheetId="8" r:id="rId7"/>
     <sheet name="Week 8" sheetId="9" r:id="rId8"/>
     <sheet name="Week 9" sheetId="10" r:id="rId9"/>
-    <sheet name="Template" sheetId="1" r:id="rId10"/>
+    <sheet name="Week 10" sheetId="11" r:id="rId10"/>
+    <sheet name="Template" sheetId="1" r:id="rId11"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="74">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -444,6 +445,24 @@
   </si>
   <si>
     <t>Additional security measures include role-based access control, password hashing with a strong algorithm, input validation, SQL injection prevention through parameterized queries, secure HTTP headers, rate limiting, file upload validation, audit logging, and HTTPS communication. I decided to combine JWT authentication with role-based authorization, secure password hashing, and comprehensive audit logs to improve overall platform security.</t>
+  </si>
+  <si>
+    <t>System Testing and Validation</t>
+  </si>
+  <si>
+    <t>Final Deployment and Documentation</t>
+  </si>
+  <si>
+    <t>FreshConnect is approaching the final development stage, and I would like to verify that all functional modules work correctly before project submission. The system includes authentication, supplier management, procurement, inventory, logistics, notifications, dashboards, and AI-assisted decision support. What testing strategy should I follow to validate both functional correctness and overall system quality within the limited time of a university project?</t>
+  </si>
+  <si>
+    <t>Before completing FreshConnect, I need to prepare the project for demonstration and future maintenance. Besides deploying the frontend and backend, I also need to organize technical documentation for developers and project stakeholders. What deployment preparation and technical documentation should be completed to ensure the project is easy to demonstrate, maintain, and further develop after the semester ends?</t>
+  </si>
+  <si>
+    <t>The testing strategy should combine unit testing for critical business logic, integration testing for API communication, and end-to-end testing for major user workflows. Functional testing should focus on authentication, purchasing, inventory updates, logistics operations, and AI recommendation generation. I decided to prioritize testing the most important business workflows while manually validating AI-generated recommendations using realistic sample data.</t>
+  </si>
+  <si>
+    <t>The project should include deployment instructions, environment configuration, database setup scripts, API documentation, system architecture diagrams, database schema, user manuals, and AI module descriptions. Configuration values should be stored in environment variables instead of source code. I decided to prepare complete technical documentation together with deployment instructions so that the project can be demonstrated smoothly and maintained more easily in the future.</t>
   </si>
 </sst>
 </file>
@@ -932,6 +951,63 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{997D88F2-4829-48F6-8370-DAAF2FDACAD4}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="25.75" customWidth="1"/>
+    <col min="3" max="3" width="76.25" customWidth="1"/>
+    <col min="4" max="4" width="88.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
